--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486923_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486923_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.75</v>
+        <v>7.3119</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7606</v>
+        <v>4.8265</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9894</v>
+        <v>2.4855</v>
       </c>
       <c r="G2" t="n">
         <v>5.4503</v>
@@ -610,13 +610,13 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9506</v>
+        <v>0.5125</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4648</v>
+        <v>0.5306</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4858</v>
+        <v>-0.0181</v>
       </c>
       <c r="V2" t="n">
         <v>0.9384</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. GATELL SANZ</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3128</v>
+        <v>4.7152</v>
       </c>
       <c r="E3" t="n">
-        <v>2.815</v>
+        <v>4.6984</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4977</v>
+        <v>0.0168</v>
       </c>
       <c r="G3" t="n">
-        <v>4.475</v>
+        <v>4.2365</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72</v>
+        <v>2.3682</v>
       </c>
       <c r="I3" t="n">
-        <v>3.755</v>
+        <v>1.8683</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5893</v>
+        <v>5.7609</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9056999999999999</v>
+        <v>3.2221</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6837</v>
+        <v>2.5388</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8857</v>
+        <v>-1.5245</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1856</v>
+        <v>-0.8539</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0713</v>
+        <v>-0.6706</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2588</v>
+        <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>2.577</v>
+        <v>-0.0901</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1539</v>
+        <v>0.4221</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4231</v>
+        <v>-0.5121</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1088</v>
+        <v>-0.4579</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1786</v>
+        <v>-0.4579</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>J. JIMÉNEZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9114</v>
+        <v>4.223</v>
       </c>
       <c r="E4" t="n">
-        <v>4.28</v>
+        <v>2.0583</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3685</v>
+        <v>2.1647</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2365</v>
+        <v>1.3922</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3682</v>
+        <v>-0.3309</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8683</v>
+        <v>1.7231</v>
       </c>
       <c r="J4" t="n">
-        <v>5.7609</v>
+        <v>1.4253</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2221</v>
+        <v>-0.0871</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5388</v>
+        <v>1.5124</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5245</v>
+        <v>-0.0331</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8539</v>
+        <v>-0.2438</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6706</v>
+        <v>0.2107</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0267</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8938</v>
+        <v>-0.0542</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0037</v>
+        <v>0.089</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8975</v>
+        <v>-0.1431</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4579</v>
+        <v>3.2957</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4579</v>
+        <v>2.5975</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ JIMÉNEZ</t>
+          <t>E. GATELL SANZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5434</v>
+        <v>3.5989</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2602</v>
+        <v>1.6644</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2832</v>
+        <v>1.9345</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3922</v>
+        <v>4.475</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3309</v>
+        <v>0.72</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7231</v>
+        <v>3.755</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4253</v>
+        <v>3.5893</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0871</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5124</v>
+        <v>2.6837</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0331</v>
+        <v>0.8857</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2438</v>
+        <v>-0.1856</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2107</v>
+        <v>1.0713</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4107</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>-4.1068</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6427</v>
+        <v>2.2588</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7337</v>
+        <v>0.8631</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7091</v>
+        <v>1.0032</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0246</v>
+        <v>-0.1401</v>
       </c>
       <c r="V5" t="n">
-        <v>3.2957</v>
+        <v>0.1088</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5975</v>
+        <v>1.1786</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6982</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6703</v>
+        <v>2.1965</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6016</v>
+        <v>0.7721</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0687</v>
+        <v>1.4244</v>
       </c>
       <c r="G6" t="n">
         <v>1.0023</v>
@@ -922,13 +922,13 @@
         <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1267</v>
+        <v>-0.6005</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0041</v>
+        <v>0.1664</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1226</v>
+        <v>-0.7669</v>
       </c>
       <c r="V6" t="n">
         <v>1.1786</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2414</v>
+        <v>0.234</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8673</v>
+        <v>-0.6969</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1087</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>0.7938</v>
@@ -1000,13 +1000,13 @@
         <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2689</v>
+        <v>0.2616</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0077</v>
+        <v>0.1782</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2612</v>
+        <v>0.0834</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.007</v>
+        <v>-0.1158</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0244</v>
+        <v>0.7378</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0314</v>
+        <v>-0.8536</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4277</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01</v>
+        <v>-0.0988</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4493</v>
+        <v>0.1626</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4393</v>
+        <v>-0.2615</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6817</v>
+        <v>-0.6001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3713</v>
+        <v>-1.2009</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6897</v>
+        <v>0.6008</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1304</v>
@@ -1156,13 +1156,13 @@
         <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1406</v>
+        <v>-0.0591</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3875</v>
+        <v>-0.217</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2469</v>
+        <v>0.158</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>O. ALVARADO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0625</v>
+        <v>-0.9198</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0604</v>
+        <v>-2.424</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0021</v>
+        <v>1.5042</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.255</v>
+        <v>1.0657</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5446</v>
+        <v>-0.0815</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7997</v>
+        <v>1.1472</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0095</v>
+        <v>0.4857</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2069</v>
+        <v>-0.1718</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1974</v>
+        <v>0.6575</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2645</v>
+        <v>0.58</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6623</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3977</v>
+        <v>0.4897</v>
       </c>
       <c r="P10" t="n">
-        <v>0.616</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2449</v>
+        <v>-0.3428</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9568</v>
+        <v>0.1704</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2016</v>
+        <v>-0.5132</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. ALVARADO RODRIGUEZ</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7664</v>
+        <v>-1.0733</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9742</v>
+        <v>-0.3084</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2078</v>
+        <v>-0.7649</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0657</v>
+        <v>-0.255</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0815</v>
+        <v>0.5446</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1472</v>
+        <v>-0.7997</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4857</v>
+        <v>0.0095</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1718</v>
+        <v>1.2069</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6575</v>
+        <v>-1.1974</v>
       </c>
       <c r="M11" t="n">
-        <v>0.58</v>
+        <v>-0.2645</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.6623</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4897</v>
+        <v>0.3977</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1894</v>
+        <v>-0.2557</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3798</v>
+        <v>0.7088</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8096</v>
+        <v>-0.9645</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>18.9117</v>
+        <v>19.5705</v>
       </c>
       <c r="E12" t="n">
-        <v>9.4686</v>
+        <v>10.1273</v>
       </c>
       <c r="F12" t="n">
-        <v>9.443199999999999</v>
+        <v>9.443300000000001</v>
       </c>
       <c r="G12" t="n">
         <v>17.6027</v>
@@ -1390,19 +1390,19 @@
         <v>13.3471</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5226000000000001</v>
+        <v>0.1359999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5557</v>
+        <v>3.2143</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.0782</v>
+        <v>-3.0781</v>
       </c>
       <c r="V12" t="n">
         <v>3.885</v>
       </c>
       <c r="W12" t="n">
-        <v>5.3263</v>
+        <v>5.326300000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-1.4413</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0262</v>
+        <v>2.6488</v>
       </c>
       <c r="E13" t="n">
-        <v>2.756</v>
+        <v>1.3962</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2701</v>
+        <v>1.2527</v>
       </c>
       <c r="G13" t="n">
         <v>0.9267</v>
@@ -1468,13 +1468,13 @@
         <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>2.619</v>
+        <v>1.2417</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4755</v>
+        <v>1.1157</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1435</v>
+        <v>0.126</v>
       </c>
       <c r="V13" t="n">
         <v>0.4805</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2745</v>
+        <v>1.9249</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7385</v>
+        <v>2.8431</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.464</v>
+        <v>-0.9183</v>
       </c>
       <c r="G14" t="n">
         <v>1.6121</v>
@@ -1546,13 +1546,13 @@
         <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2678</v>
+        <v>0.3825</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0464</v>
+        <v>0.151</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3142</v>
+        <v>0.2316</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4805</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0234</v>
+        <v>0.5142</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0448</v>
+        <v>-0.3861</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0682</v>
+        <v>0.9004</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6674</v>
+        <v>1.0722</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6069</v>
+        <v>0.9277</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0605</v>
+        <v>0.1445</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5600000000000001</v>
+        <v>1.8341</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0584</v>
+        <v>2.2031</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.369</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1074</v>
+        <v>-0.7619</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6653</v>
+        <v>-1.2753</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5579</v>
+        <v>0.5134</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2053</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.2855</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2053</v>
+        <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4854</v>
+        <v>0.6392</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5152</v>
+        <v>0.825</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0298</v>
+        <v>-0.1858</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5458</v>
+        <v>-0.0969</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8539</v>
+        <v>-0.254</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3996</v>
+        <v>0.1571</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2749</v>
+        <v>-0.6674</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.32</v>
+        <v>-0.6069</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9549</v>
+        <v>-0.0605</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0319</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.126</v>
+        <v>0.0584</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1579</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3068</v>
+        <v>-0.1074</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.194</v>
+        <v>-0.6653</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1127</v>
+        <v>0.5579</v>
       </c>
       <c r="P16" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5238</v>
+        <v>0.3651</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6701</v>
+        <v>0.306</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1463</v>
+        <v>0.0592</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1176</v>
+        <v>-0.6783</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2229</v>
+        <v>0.5401</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1053</v>
+        <v>-1.2184</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0722</v>
+        <v>-2.2749</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9277</v>
+        <v>-1.32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1445</v>
+        <v>-0.9549</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8341</v>
+        <v>0.0319</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2031</v>
+        <v>-0.126</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.369</v>
+        <v>0.1579</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7619</v>
+        <v>-2.3068</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2753</v>
+        <v>-1.194</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5134</v>
+        <v>-1.1127</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2855</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9926</v>
+        <v>0.3913</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0118</v>
+        <v>0.3563</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9808</v>
+        <v>0.035</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2402</v>
+        <v>0.5893</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8015</v>
+        <v>-1.1895</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6353</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1662</v>
+        <v>-0.6589</v>
       </c>
       <c r="G18" t="n">
         <v>-2.5736</v>
@@ -1858,13 +1858,13 @@
         <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8706</v>
+        <v>-0.2587</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4652</v>
+        <v>-0.3606</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4055</v>
+        <v>0.1019</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3236</v>
+        <v>-1.4903</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4948</v>
+        <v>-1.7625</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1712</v>
+        <v>0.2723</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0458</v>
@@ -1936,13 +1936,13 @@
         <v>1.6427</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9554</v>
+        <v>-0.1221</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.899</v>
+        <v>-0.1668</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0564</v>
+        <v>0.0447</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9384</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4089</v>
+        <v>-2.0863</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3505</v>
+        <v>-1.4551</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0584</v>
+        <v>-0.6313</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7392</v>
@@ -2014,13 +2014,13 @@
         <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2769</v>
+        <v>0.5995</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5034</v>
+        <v>0.3988</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2265</v>
+        <v>0.2007</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1786</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5314</v>
+        <v>-4.1944</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9998</v>
+        <v>-1.4843</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5316</v>
+        <v>-2.7101</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.6544</v>
+        <v>-2.173</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7232</v>
+        <v>-2.6309</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9312</v>
+        <v>0.4579</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.4106</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4764</v>
+        <v>-1.2974</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9342</v>
+        <v>1.2234</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2438</v>
+        <v>-2.0991</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2468</v>
+        <v>-1.3335</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.997</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P21" t="n">
         <v>-0.616</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1579</v>
+        <v>-0.2267</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8749</v>
+        <v>-0.1783</v>
       </c>
       <c r="U21" t="n">
-        <v>0.283</v>
+        <v>-0.0484</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0082</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4628</v>
+        <v>-4.56</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6935</v>
+        <v>-3.1504</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7694</v>
+        <v>-1.4096</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.173</v>
+        <v>-3.6544</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6309</v>
+        <v>-0.7232</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4579</v>
+        <v>-2.9312</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-2.4106</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2974</v>
+        <v>-0.4764</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2234</v>
+        <v>-1.9342</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0991</v>
+        <v>-1.2438</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3335</v>
+        <v>-0.2468</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.997</v>
       </c>
       <c r="P22" t="n">
         <v>-0.616</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4952</v>
+        <v>1.1293</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3875</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1077</v>
+        <v>0.405</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1786</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.0442</v>
+        <v>-6.2171</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.35</v>
+        <v>-5.1994</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6942</v>
+        <v>-1.0177</v>
       </c>
       <c r="G23" t="n">
         <v>-6.0853</v>
@@ -2248,13 +2248,13 @@
         <v>2.2588</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9589</v>
+        <v>-0.1318</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2438</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7151</v>
+        <v>-0.0386</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.9117</v>
+        <v>-15.4249</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.443199999999999</v>
+        <v>-9.443099999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.4686</v>
+        <v>-5.9818</v>
       </c>
       <c r="G24" t="n">
         <v>-17.6026</v>
@@ -2302,10 +2302,10 @@
         <v>-0.6154000000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>2.308000000000001</v>
+        <v>2.307999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.923500000000001</v>
+        <v>-2.9235</v>
       </c>
       <c r="M24" t="n">
         <v>-16.9874</v>
@@ -2326,22 +2326,22 @@
         <v>15.4006</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5225000000000002</v>
+        <v>4.0093</v>
       </c>
       <c r="T24" t="n">
-        <v>3.078199999999999</v>
+        <v>3.0782</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.5558</v>
+        <v>0.9313</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.885000000000001</v>
+        <v>-3.885</v>
       </c>
       <c r="W24" t="n">
         <v>1.4413</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.326300000000001</v>
+        <v>-5.3263</v>
       </c>
     </row>
   </sheetData>
